--- a/ExcelTable/Enum.xlsx
+++ b/ExcelTable/Enum.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R1786265880e14078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R26e3c506486647e7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/ExcelTable/Enum.xlsx
+++ b/ExcelTable/Enum.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R26e3c506486647e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="Ra97f0460e7bb4624"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,8 +45,13 @@
       <x:color rgb="FF92400E"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,8 +78,13 @@
         <x:fgColor rgb="FFFEF3C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -90,11 +100,25 @@
         <x:color rgb="FFD1D5DB"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -110,6 +134,9 @@
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -820,6 +847,146 @@
         <x:v>점멸</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" ht="16.5" customHeight="1">
+      <x:c r="A26" s="17" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B26" s="17" t="str">
+        <x:v>SkillKey</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="str">
+        <x:v>PLAYER_BASIC_ATTACK</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="str">
+        <x:v>플레이어 기본 공격</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="16.5" customHeight="1">
+      <x:c r="A27" s="17" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B27" s="17" t="str">
+        <x:v>SkillKey</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="str">
+        <x:v>SLIME_CONTACT_DAMAGE</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="str">
+        <x:v>슬라임 접촉 피해</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="16.5" customHeight="1">
+      <x:c r="A28" s="17" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B28" s="17" t="str">
+        <x:v>SkillKey</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="str">
+        <x:v>SLIME_ACTIVE_ATTACK</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="n">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="str">
+        <x:v>슬라임 능동 공격</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="16.5" customHeight="1">
+      <x:c r="A29" s="17" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B29" s="17" t="str">
+        <x:v>SkillHitOriginType</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="str">
+        <x:v>SELF</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="str">
+        <x:v>나</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="16.5" customHeight="1">
+      <x:c r="A30" s="17" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B30" s="17" t="str">
+        <x:v>SkillHitOriginType</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="str">
+        <x:v>TARGET</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="str">
+        <x:v>대상</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="16.5" customHeight="1">
+      <x:c r="A31" s="17" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B31" s="17" t="str">
+        <x:v>SkillHitShapeType</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="str">
+        <x:v>CIRCLE</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="str">
+        <x:v>원</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="16.5" customHeight="1">
+      <x:c r="A32" s="17" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B32" s="17" t="str">
+        <x:v>SkillHitShapeType</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="str">
+        <x:v>RECTANGLE</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="str">
+        <x:v>사각형</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
